--- a/Taches.xlsx
+++ b/Taches.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_jv\Projet1_Jeux_Video\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Nouveau dossier\Projet1_Jeux_Video\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4730937C-F0EE-4D6B-AFFB-B5F818A242CB}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17A5164-0C44-4963-8492-4F30C520D43D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7008" yWindow="1428" windowWidth="16032" windowHeight="12252" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
+    <workbookView xWindow="7010" yWindow="1430" windowWidth="16030" windowHeight="12250" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -23,17 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="58">
   <si>
     <t>Fonctionnalites</t>
   </si>
@@ -299,6 +294,24 @@
   </si>
   <si>
     <t>Pas commencé</t>
+  </si>
+  <si>
+    <t>Antoine</t>
+  </si>
+  <si>
+    <t>Charlee</t>
+  </si>
+  <si>
+    <t>nb vies + vitesse</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>****</t>
+  </si>
+  <si>
+    <t>tout le monde</t>
   </si>
 </sst>
 </file>
@@ -428,7 +441,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -451,6 +464,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -503,9 +527,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -517,6 +538,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -854,319 +878,366 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45B5B6CB-DB26-432C-9FC7-91B77E13F469}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.21875" customWidth="1"/>
-    <col min="2" max="2" width="106.44140625" customWidth="1"/>
-    <col min="3" max="3" width="57.109375" customWidth="1"/>
-    <col min="4" max="4" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="77.6640625" customWidth="1"/>
+    <col min="1" max="1" width="41.1796875" customWidth="1"/>
+    <col min="2" max="2" width="106.453125" customWidth="1"/>
+    <col min="3" max="3" width="57.08984375" customWidth="1"/>
+    <col min="4" max="4" width="36.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="77.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:5" ht="55.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="323.39999999999998" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="323.39999999999998" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="15"/>
+      <c r="C2" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>52</v>
+      </c>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="306" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="314.5" x14ac:dyDescent="0.5">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="16"/>
+      <c r="C3" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="54.6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="56" x14ac:dyDescent="0.5">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="15"/>
+      <c r="C4" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" ht="59.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="59.4" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="16"/>
+      <c r="C5" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" ht="220.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="220.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="14" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="15"/>
+      <c r="C6" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="36.6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.5">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="16"/>
+      <c r="C7" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" ht="54.6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" ht="56" x14ac:dyDescent="0.5">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="15"/>
+      <c r="C8" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="17"/>
+      <c r="C9" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="54.6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" ht="56" x14ac:dyDescent="0.5">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="15"/>
+      <c r="C10" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" ht="108.6" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" ht="112.5" x14ac:dyDescent="0.6">
       <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="17"/>
+      <c r="C11" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:5" ht="36" x14ac:dyDescent="0.6">
       <c r="A12" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="20" t="s">
         <v>48</v>
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5" ht="36.6" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.6">
       <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="16"/>
+      <c r="C13" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5" ht="36.6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" ht="36" x14ac:dyDescent="0.6">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="15"/>
+      <c r="C14" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" ht="36.6" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" ht="38.5" x14ac:dyDescent="0.6">
       <c r="A15" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="17"/>
+      <c r="C15" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" ht="36.6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" ht="38.5" x14ac:dyDescent="0.6">
       <c r="A16" s="6" t="s">
         <v>31</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="18"/>
+      <c r="C16" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" ht="36.6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" ht="36" x14ac:dyDescent="0.6">
       <c r="A17" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="16"/>
+      <c r="C17" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" ht="36.6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="36" x14ac:dyDescent="0.5">
       <c r="A18" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="18"/>
+      <c r="C18" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>52</v>
+      </c>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5" ht="36.6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" ht="36" x14ac:dyDescent="0.5">
       <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="16"/>
+      <c r="C19" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5" ht="54.6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" ht="56" x14ac:dyDescent="0.5">
       <c r="A20" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="15"/>
+      <c r="C20" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>55</v>
+      </c>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="1:5" ht="72" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="74" x14ac:dyDescent="0.45">
       <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="9"/>
+      <c r="C21" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>52</v>
+      </c>
       <c r="E21" s="9"/>
     </row>
-    <row r="22" spans="1:5" ht="54" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="55.5" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" spans="1:5" ht="82.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C22" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="82.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="9"/>
+      <c r="C23" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>55</v>
+      </c>
       <c r="E23" s="9"/>
     </row>
   </sheetData>

--- a/Taches.xlsx
+++ b/Taches.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Nouveau dossier\Projet1_Jeux_Video\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_jv\Projet1_Jeux_Video\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17A5164-0C44-4963-8492-4F30C520D43D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802D5BE2-6B86-4943-B8DC-33257F5B259C}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7010" yWindow="1430" windowWidth="16030" windowHeight="12250" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="59">
   <si>
     <t>Fonctionnalites</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>tout le monde</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tous ont 4 animations de déplacement (une pour chaque direction).:ok pour zombie</t>
   </si>
 </sst>
 </file>
@@ -879,16 +882,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45B5B6CB-DB26-432C-9FC7-91B77E13F469}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.1796875" customWidth="1"/>
-    <col min="2" max="2" width="106.453125" customWidth="1"/>
-    <col min="3" max="3" width="57.08984375" customWidth="1"/>
-    <col min="4" max="4" width="36.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="77.6328125" customWidth="1"/>
+    <col min="1" max="1" width="41.21875" customWidth="1"/>
+    <col min="2" max="2" width="106.44140625" customWidth="1"/>
+    <col min="3" max="3" width="57.109375" customWidth="1"/>
+    <col min="4" max="4" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="77.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="55.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -905,7 +908,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="323.39999999999998" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" ht="323.39999999999998" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -920,7 +923,7 @@
       </c>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="314.5" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:5" ht="306" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -935,7 +938,7 @@
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="56" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:5" ht="54.6" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -950,7 +953,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" ht="59.4" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:5" ht="59.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -965,7 +968,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" ht="220.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:5" ht="220.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>12</v>
       </c>
@@ -980,7 +983,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:5" ht="36.6" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -995,7 +998,7 @@
       </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" ht="56" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:5" ht="54.6" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -1010,7 +1013,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
@@ -1025,7 +1028,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="56" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:5" ht="54.6" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1040,7 +1043,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" ht="112.5" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:5" ht="150" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
@@ -1048,14 +1051,16 @@
         <v>22</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:5" ht="36" x14ac:dyDescent="0.6">
+      <c r="E11" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
       <c r="A12" s="5" t="s">
         <v>23</v>
       </c>
@@ -1070,7 +1075,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
       <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
@@ -1085,7 +1090,7 @@
       </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5" ht="36" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -1100,7 +1105,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" ht="38.5" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:5" ht="37.799999999999997" x14ac:dyDescent="0.5">
       <c r="A15" s="4" t="s">
         <v>29</v>
       </c>
@@ -1115,7 +1120,7 @@
       </c>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" ht="38.5" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:5" ht="37.799999999999997" x14ac:dyDescent="0.5">
       <c r="A16" s="6" t="s">
         <v>31</v>
       </c>
@@ -1130,7 +1135,7 @@
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:6" ht="36" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:6" ht="36.6" x14ac:dyDescent="0.5">
       <c r="A17" s="3" t="s">
         <v>33</v>
       </c>
@@ -1145,7 +1150,7 @@
       </c>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:6" ht="36" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:6" ht="36.6" x14ac:dyDescent="0.4">
       <c r="A18" s="6" t="s">
         <v>35</v>
       </c>
@@ -1160,7 +1165,7 @@
       </c>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:6" ht="36" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:6" ht="36.6" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
@@ -1175,7 +1180,7 @@
       </c>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="56" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:6" ht="54.6" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
         <v>39</v>
       </c>
@@ -1190,7 +1195,7 @@
       </c>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="1:6" ht="74" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" ht="72" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
@@ -1205,7 +1210,7 @@
       </c>
       <c r="E21" s="9"/>
     </row>
-    <row r="22" spans="1:6" ht="55.5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" ht="54" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>43</v>
       </c>
@@ -1225,7 +1230,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="82.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="82.2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>45</v>
       </c>

--- a/Taches.xlsx
+++ b/Taches.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Nouveau dossier\Projet1_Jeux_Video\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chacy\My Shit\Projet1_Jeux_Video\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17A5164-0C44-4963-8492-4F30C520D43D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0764F5B-01F9-4A21-89DA-7CF035D32C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7010" yWindow="1430" windowWidth="16030" windowHeight="12250" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="59">
   <si>
     <t>Fonctionnalites</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>tout le monde</t>
+  </si>
+  <si>
+    <t>Apparaît et bouge avec le joueur, reste à faire collisions</t>
   </si>
 </sst>
 </file>
@@ -479,9 +482,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -540,6 +542,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -582,9 +596,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -622,7 +636,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -728,7 +742,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -870,7 +884,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -879,366 +893,368 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45B5B6CB-DB26-432C-9FC7-91B77E13F469}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="41.1796875" customWidth="1"/>
-    <col min="2" max="2" width="106.453125" customWidth="1"/>
-    <col min="3" max="3" width="57.08984375" customWidth="1"/>
-    <col min="4" max="4" width="36.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="77.6328125" customWidth="1"/>
+    <col min="1" max="1" width="41.140625" customWidth="1"/>
+    <col min="2" max="2" width="106.42578125" customWidth="1"/>
+    <col min="3" max="3" width="57.140625" customWidth="1"/>
+    <col min="4" max="4" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="77.5703125" style="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="55.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:5" ht="55.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="323.39999999999998" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:5" ht="323.45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" ht="314.5" x14ac:dyDescent="0.5">
-      <c r="A3" s="3" t="s">
+      <c r="E2" s="22"/>
+    </row>
+    <row r="3" spans="1:5" ht="337.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="16" t="s">
+      <c r="C3" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" ht="56" x14ac:dyDescent="0.5">
-      <c r="A4" s="2" t="s">
+      <c r="E3" s="23"/>
+    </row>
+    <row r="4" spans="1:5" ht="57" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="15" t="s">
+      <c r="C4" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" ht="59.4" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="3" t="s">
+      <c r="E4" s="22"/>
+    </row>
+    <row r="5" spans="1:5" ht="59.45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="15" t="s">
+      <c r="C5" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" ht="220.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="14" t="s">
+      <c r="E5" s="23"/>
+    </row>
+    <row r="6" spans="1:5" ht="220.7" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="15" t="s">
+      <c r="C6" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.5">
-      <c r="A7" s="3" t="s">
+      <c r="E6" s="22"/>
+    </row>
+    <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="15" t="s">
+      <c r="C7" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" ht="56" x14ac:dyDescent="0.5">
-      <c r="A8" s="2" t="s">
+      <c r="E7" s="23"/>
+    </row>
+    <row r="8" spans="1:5" ht="57" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="15" t="s">
+      <c r="C8" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="4" t="s">
+      <c r="E8" s="22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="15" t="s">
+      <c r="C9" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" ht="56" x14ac:dyDescent="0.5">
-      <c r="A10" s="2" t="s">
+      <c r="E9" s="23"/>
+    </row>
+    <row r="10" spans="1:5" ht="57" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="15" t="s">
+      <c r="C10" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" ht="112.5" x14ac:dyDescent="0.6">
-      <c r="A11" s="4" t="s">
+      <c r="E10" s="22"/>
+    </row>
+    <row r="11" spans="1:5" ht="132.75" x14ac:dyDescent="0.4">
+      <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="20" t="s">
+      <c r="C11" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:5" ht="36" x14ac:dyDescent="0.6">
-      <c r="A12" s="5" t="s">
+      <c r="E11" s="23"/>
+    </row>
+    <row r="12" spans="1:5" ht="36" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.6">
-      <c r="A13" s="3" t="s">
+      <c r="E12" s="22"/>
+    </row>
+    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="20" t="s">
+      <c r="C13" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" ht="36" x14ac:dyDescent="0.6">
-      <c r="A14" s="2" t="s">
+      <c r="E13" s="23"/>
+    </row>
+    <row r="14" spans="1:5" ht="36" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="20" t="s">
+      <c r="C14" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:5" ht="38.5" x14ac:dyDescent="0.6">
-      <c r="A15" s="4" t="s">
+      <c r="E14" s="22"/>
+    </row>
+    <row r="15" spans="1:5" ht="57.75" x14ac:dyDescent="0.4">
+      <c r="A15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="20" t="s">
+      <c r="C15" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" ht="38.5" x14ac:dyDescent="0.6">
-      <c r="A16" s="6" t="s">
+      <c r="E15" s="23"/>
+    </row>
+    <row r="16" spans="1:5" ht="57.75" x14ac:dyDescent="0.4">
+      <c r="A16" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="20" t="s">
+      <c r="C16" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" ht="36" x14ac:dyDescent="0.6">
-      <c r="A17" s="3" t="s">
+      <c r="E16" s="22"/>
+    </row>
+    <row r="17" spans="1:6" ht="39" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="20" t="s">
+      <c r="C17" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" ht="36" x14ac:dyDescent="0.5">
-      <c r="A18" s="6" t="s">
+      <c r="E17" s="23"/>
+    </row>
+    <row r="18" spans="1:6" ht="36" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="17" t="s">
+      <c r="C18" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" ht="36" x14ac:dyDescent="0.5">
-      <c r="A19" s="3" t="s">
+      <c r="E18" s="22"/>
+    </row>
+    <row r="19" spans="1:6" ht="36" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="16" t="s">
+      <c r="C19" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:6" ht="56" x14ac:dyDescent="0.5">
-      <c r="A20" s="2" t="s">
+      <c r="E19" s="23"/>
+    </row>
+    <row r="20" spans="1:6" ht="57" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="15" t="s">
+      <c r="C20" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="1:6" ht="74" x14ac:dyDescent="0.45">
-      <c r="A21" s="3" t="s">
+      <c r="E20" s="22"/>
+    </row>
+    <row r="21" spans="1:6" ht="75" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="9" t="s">
+      <c r="C21" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E21" s="9"/>
-    </row>
-    <row r="22" spans="1:6" ht="55.5" x14ac:dyDescent="0.45">
-      <c r="A22" s="2" t="s">
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" spans="1:6" ht="56.25" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="7" t="s">
+      <c r="C22" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F22" s="21" t="s">
+      <c r="F22" s="20" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="82.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:6" ht="82.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="9" t="s">
+      <c r="C23" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E23" s="9"/>
+      <c r="E23" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{69A9896E-8EAC-4EAC-8BD0-8B557D602AA3}"/>

--- a/Taches.xlsx
+++ b/Taches.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Nouveau dossier\Projet1_Jeux_Video\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DDJV\Projet1_Jeux_Video\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17A5164-0C44-4963-8492-4F30C520D43D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87EA834-6DC1-459D-89A9-6B5ED08ED159}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7010" yWindow="1430" windowWidth="16030" windowHeight="12250" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
   </bookViews>
@@ -45,19 +45,6 @@
     <t>Texte</t>
   </si>
   <si>
-    <t xml:space="preserve">Niveau
-Un seul niveau bien conçu est demandé. On doit prendre soin d’avoir un visuel varié et soigné composé de plusieurs couches d’images. 
-1) Arrière-plan sur lequel le joueur marche (exemple : composition de gazon ou de terre).
-2) Doodads d’arrière-plan : petits objets décoratifs : plantes, cailloux, fleurs, etc.
-a. Au moins 3 différents non animés et fixe.
-b. Au moins 1 différent animé par du vent variable : ed :windsystem
-3) Doodads d’avant-plan animé : on doit voir minimum 2 entités (Exemple : nuages et oiseaux) se promener de gauche à droite à des vitesse variables. Ils doivent être petits ou semi-transparent afin de ne pas nuire à la visibilité du jeu.
-La limites de mouvement est de 3x3 la largeur de la grosseur de caméra que vous choisirez. Si le joueur dépasse cette limite, il est éliminé immédiatement.
-Cependant, quand le joueur près du bord de la carte, le visuel doit être adéquat pour 4x4 la largeur de la caméra.
-Exemple de conception adéquate : Une île bordée par de l’eau. Un donjon entouré de pics, une cave entourée de bras animées, etc.
-</t>
-  </si>
-  <si>
     <t>Joueur</t>
   </si>
   <si>
@@ -194,6 +181,91 @@
 • Barre d’expérience dans le haut de l’écran ou au-dessus du joueur.</t>
   </si>
   <si>
+    <t>Eddy</t>
+  </si>
+  <si>
+    <t>Commentaires</t>
+  </si>
+  <si>
+    <t>En cours</t>
+  </si>
+  <si>
+    <t>Pas commencé</t>
+  </si>
+  <si>
+    <t>Antoine</t>
+  </si>
+  <si>
+    <t>Charlee</t>
+  </si>
+  <si>
+    <t>nb vies + vitesse</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>****</t>
+  </si>
+  <si>
+    <t>tout le monde</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Niveau
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Un seul niveau bien conçu est demandé. On doit prendre soin d’avoir un visuel varié et soigné composé de plusieurs couches d’images. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1) Arrière-plan sur lequel le joueur marche (exemple : composition de gazon ou de terre).</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2) Doodads d’arrière-plan : petits objets décoratifs : plantes, cailloux, fleurs, etc.
+a. Au moins 3 différents non animés et fixe.
+b. Au moins 1 différent animé par du vent variable : ed :windsystem
+3) Doodads d’avant-plan animé : on doit voir minimum 2 entités (Exemple : nuages et oiseaux) se promener de gauche à droite à des vitesse variables. Ils doivent être petits ou semi-transparent afin de ne pas nuire à la visibilité du jeu.
+La limites de mouvement est de 3x3 la largeur de la grosseur de caméra que vous choisirez. Si le joueur dépasse cette limite, il est éliminé immédiatement.
+Cependant, quand le joueur près du bord de la carte, le visuel doit être adéquat pour 4x4 la largeur de la caméra.
+Exemple de conception adéquate : Une île bordée par de l’eau. Un donjon entouré de pics, une cave entourée de bras animées, etc.
+</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -215,10 +287,90 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Attachez une Camera2D au joueur. Le joueur a 5 points de vie et commencera la partie avec une seule arme au choix. Si le joueur sort de la carte, il est automatiquement éliminé.
-• Animation
-o Animation unique quand ne bouge pas.
-o 4 animations différentes pour les 4 directions. Trouvez un tween pour agrémenter le mouvement.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Attachez une Camera2D au joueur.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Le joueur a 5 points de vie et commencera la partie avec une seule arme au choix. Si le joueur sort de la carte, il est automatiquement éliminé.
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Animation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+o </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Animation unique quand ne bouge pas.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+o </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4 animations différentes pour les 4 directions.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Trouvez un tween pour agrémenter le mouvement.
 o Animation unique lors d’une blessure accompagnée d’un tween.
 o Pour l’élimination, réutilisez l’animation unique de quand il ne bouge pas mais accompagnez le tout d’un tween et coloriez le joueur en rouge.
 o Pour la victoire, réutilisez l’animation unique de quand il ne bouge pas mais accompagnez le tout d’un tween et coloriez le joueur en vert.
@@ -282,43 +434,13 @@
       <t xml:space="preserve">
 </t>
     </r>
-  </si>
-  <si>
-    <t>Eddy</t>
-  </si>
-  <si>
-    <t>Commentaires</t>
-  </si>
-  <si>
-    <t>En cours</t>
-  </si>
-  <si>
-    <t>Pas commencé</t>
-  </si>
-  <si>
-    <t>Antoine</t>
-  </si>
-  <si>
-    <t>Charlee</t>
-  </si>
-  <si>
-    <t>nb vies + vitesse</t>
-  </si>
-  <si>
-    <t>Paul</t>
-  </si>
-  <si>
-    <t>****</t>
-  </si>
-  <si>
-    <t>tout le monde</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,6 +514,13 @@
       <b/>
       <sz val="26"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="9"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -902,7 +1031,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="323.39999999999998" customHeight="1" x14ac:dyDescent="0.5">
@@ -910,333 +1039,333 @@
         <v>3</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" ht="314.5" x14ac:dyDescent="0.5">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="56" x14ac:dyDescent="0.5">
       <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="C4" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>51</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>53</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" ht="59.4" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="C5" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>51</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>53</v>
       </c>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="220.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>51</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>53</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.5">
       <c r="A7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="C7" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>51</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>53</v>
       </c>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" ht="56" x14ac:dyDescent="0.5">
       <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>16</v>
-      </c>
       <c r="C8" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>51</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>53</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>18</v>
-      </c>
       <c r="C9" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>51</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>53</v>
       </c>
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" ht="56" x14ac:dyDescent="0.5">
       <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>20</v>
-      </c>
       <c r="C10" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>51</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>53</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" ht="112.5" x14ac:dyDescent="0.6">
       <c r="A11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>22</v>
-      </c>
       <c r="C11" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" ht="36" x14ac:dyDescent="0.6">
       <c r="A12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>24</v>
-      </c>
       <c r="C12" s="18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.6">
       <c r="A13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>26</v>
-      </c>
       <c r="C13" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5" ht="36" x14ac:dyDescent="0.6">
       <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="C14" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5" ht="38.5" x14ac:dyDescent="0.6">
       <c r="A15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>30</v>
-      </c>
       <c r="C15" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:5" ht="38.5" x14ac:dyDescent="0.6">
       <c r="A16" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>32</v>
-      </c>
       <c r="C16" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:6" ht="36" x14ac:dyDescent="0.6">
       <c r="A17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>34</v>
-      </c>
       <c r="C17" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:6" ht="36" x14ac:dyDescent="0.5">
       <c r="A18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>36</v>
-      </c>
       <c r="C18" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19" spans="1:6" ht="36" x14ac:dyDescent="0.5">
       <c r="A19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>38</v>
-      </c>
       <c r="C19" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E19" s="1"/>
     </row>
     <row r="20" spans="1:6" ht="56" x14ac:dyDescent="0.5">
       <c r="A20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>40</v>
-      </c>
       <c r="C20" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:6" ht="74" x14ac:dyDescent="0.45">
       <c r="A21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>42</v>
-      </c>
       <c r="C21" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E21" s="9"/>
     </row>
     <row r="22" spans="1:6" ht="55.5" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>44</v>
-      </c>
       <c r="C22" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="82.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>46</v>
-      </c>
       <c r="C23" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E23" s="9"/>
     </row>

--- a/Taches.xlsx
+++ b/Taches.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_jv\Projet1_Jeux_Video\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DDJV\Projet\Projet1_Jeux_Video\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802D5BE2-6B86-4943-B8DC-33257F5B259C}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C325F0F8-0376-4F67-A099-A65F99BE273E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="60">
   <si>
     <t>Fonctionnalites</t>
   </si>
@@ -316,6 +316,9 @@
   <si>
     <t xml:space="preserve"> Tous ont 4 animations de déplacement (une pour chaque direction).:ok pour zombie</t>
   </si>
+  <si>
+    <t>Terminé</t>
+  </si>
 </sst>
 </file>
 
@@ -400,7 +403,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -443,6 +446,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -482,7 +491,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -544,6 +553,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -882,16 +894,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45B5B6CB-DB26-432C-9FC7-91B77E13F469}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.21875" customWidth="1"/>
-    <col min="2" max="2" width="106.44140625" customWidth="1"/>
-    <col min="3" max="3" width="57.109375" customWidth="1"/>
-    <col min="4" max="4" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="77.6640625" customWidth="1"/>
+    <col min="1" max="1" width="41.1796875" customWidth="1"/>
+    <col min="2" max="2" width="106.453125" customWidth="1"/>
+    <col min="3" max="3" width="57.08984375" customWidth="1"/>
+    <col min="4" max="4" width="36.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="77.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="55.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -908,7 +920,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="323.39999999999998" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="323.39999999999998" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -923,7 +935,7 @@
       </c>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="306" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="314.5" x14ac:dyDescent="0.5">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -938,7 +950,7 @@
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="54.6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="56" x14ac:dyDescent="0.5">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -953,7 +965,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" ht="59.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="59.4" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -968,7 +980,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" ht="220.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="220.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="14" t="s">
         <v>12</v>
       </c>
@@ -983,7 +995,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="36.6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.5">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -998,7 +1010,7 @@
       </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" ht="54.6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" ht="56" x14ac:dyDescent="0.5">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -1013,7 +1025,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
@@ -1028,7 +1040,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="54.6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" ht="56" x14ac:dyDescent="0.5">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1043,7 +1055,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" ht="150" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:5" ht="150" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
@@ -1060,7 +1072,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:5" ht="36" x14ac:dyDescent="0.6">
       <c r="A12" s="5" t="s">
         <v>23</v>
       </c>
@@ -1075,7 +1087,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.6">
       <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
@@ -1090,7 +1102,7 @@
       </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:5" ht="36" x14ac:dyDescent="0.6">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -1105,7 +1117,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" ht="37.799999999999997" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:5" ht="38.5" x14ac:dyDescent="0.6">
       <c r="A15" s="4" t="s">
         <v>29</v>
       </c>
@@ -1120,7 +1132,7 @@
       </c>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" ht="37.799999999999997" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:5" ht="38.5" x14ac:dyDescent="0.6">
       <c r="A16" s="6" t="s">
         <v>31</v>
       </c>
@@ -1135,7 +1147,7 @@
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:6" ht="36.6" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:6" ht="36" x14ac:dyDescent="0.6">
       <c r="A17" s="3" t="s">
         <v>33</v>
       </c>
@@ -1150,7 +1162,7 @@
       </c>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:6" ht="36.6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="36" x14ac:dyDescent="0.5">
       <c r="A18" s="6" t="s">
         <v>35</v>
       </c>
@@ -1165,7 +1177,7 @@
       </c>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:6" ht="36.6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" ht="36" x14ac:dyDescent="0.5">
       <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
@@ -1180,22 +1192,22 @@
       </c>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="54.6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" ht="56" x14ac:dyDescent="0.5">
       <c r="A20" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="18" t="s">
-        <v>51</v>
+      <c r="C20" s="22" t="s">
+        <v>59</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>55</v>
       </c>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="74" x14ac:dyDescent="0.45">
       <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
@@ -1210,7 +1222,7 @@
       </c>
       <c r="E21" s="9"/>
     </row>
-    <row r="22" spans="1:6" ht="54" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="55.5" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>43</v>
       </c>
@@ -1230,7 +1242,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="82.2" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="82.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
         <v>45</v>
       </c>

--- a/Taches.xlsx
+++ b/Taches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DDJV\Projet1_Jeux_Video\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87EA834-6DC1-459D-89A9-6B5ED08ED159}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E335CAA2-DAAF-4041-9903-E801ADEE11EC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7010" yWindow="1430" windowWidth="16030" windowHeight="12250" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
   </bookViews>
@@ -255,13 +255,93 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-2) Doodads d’arrière-plan : petits objets décoratifs : plantes, cailloux, fleurs, etc.
-a. Au moins 3 différents non animés et fixe.
+2) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Doodads d’arrière-plan : petits objets décoratifs : plantes, cailloux, fleurs, etc.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a. Au moins 3 différents non animés et fixe.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 b. Au moins 1 différent animé par du vent variable : ed :windsystem
 3) Doodads d’avant-plan animé : on doit voir minimum 2 entités (Exemple : nuages et oiseaux) se promener de gauche à droite à des vitesse variables. Ils doivent être petits ou semi-transparent afin de ne pas nuire à la visibilité du jeu.
-La limites de mouvement est de 3x3 la largeur de la grosseur de caméra que vous choisirez. Si le joueur dépasse cette limite, il est éliminé immédiatement.
-Cependant, quand le joueur près du bord de la carte, le visuel doit être adéquat pour 4x4 la largeur de la caméra.
-Exemple de conception adéquate : Une île bordée par de l’eau. Un donjon entouré de pics, une cave entourée de bras animées, etc.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La limites de mouvement est de 3x3 la largeur de la grosseur de caméra que vous choisirez. Si le joueur dépasse cette limite, il est éliminé immédiatement.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cependant, quand le joueur près du bord de la carte, le visuel doit être adéquat pour 4x4 la largeur de la caméra.
+Exemple de conception adéquate : Une île bordée par de l’eau. Un donjon entouré de pics, une cave entourée de bras animées, etc.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
   </si>
@@ -307,7 +387,27 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Le joueur a 5 points de vie et commencera la partie avec une seule arme au choix. Si le joueur sort de la carte, il est automatiquement éliminé.
+      <t xml:space="preserve"> Le joueur a 5 points de vie et commencera la partie avec une seule arme au choix. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Si le joueur sort de la carte, il est automatiquement éliminé.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 • </t>
     </r>
     <r>
@@ -403,7 +503,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <color theme="1"/>
+        <color theme="9"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -415,7 +515,7 @@
       <rPr>
         <u/>
         <sz val="14"/>
-        <color theme="1"/>
+        <color theme="9"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -440,7 +540,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -521,6 +621,28 @@
     <font>
       <sz val="14"/>
       <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>

--- a/Taches.xlsx
+++ b/Taches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DDJV\Projet1_Jeux_Video\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E335CAA2-DAAF-4041-9903-E801ADEE11EC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40788F3-6FDB-437A-A35C-881967C0F6A0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7010" yWindow="1430" windowWidth="16030" windowHeight="12250" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
   </bookViews>
@@ -165,9 +165,6 @@
     <t xml:space="preserve">Gestion de la partie </t>
   </si>
   <si>
-    <t>Au démarrage du jeu, le joueur est placé au centre et tout est figé jusqu’à ce qu’on appuie sur la touche espace. La partie commence alors. La partie doit durer quelques minutes au plus et terminer si le joueur est éliminé ou s’il élimine le boss. Au moment que la partie se termine, détruire tous les ennemis et figer le joueur en jouant l’animation appropriée.</t>
-  </si>
-  <si>
     <t>Progression de difficulté</t>
   </si>
   <si>
@@ -533,6 +530,28 @@
       </rPr>
       <t xml:space="preserve">
 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Au démarrage du jeu, le joueur est placé au centre et tout est figé jusqu’à ce qu’on appuie sur la touche espace. La partie commence alors. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La partie doit durer quelques minutes au plus et terminer si le joueur est éliminé ou s’il élimine le boss. Au moment que la partie se termine, détruire tous les ennemis et figer le joueur en jouant l’animation appropriée.</t>
     </r>
   </si>
 </sst>
@@ -1153,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="323.39999999999998" customHeight="1" x14ac:dyDescent="0.5">
@@ -1161,13 +1180,13 @@
         <v>3</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="15" t="s">
         <v>49</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>50</v>
       </c>
       <c r="E2" s="2"/>
     </row>
@@ -1176,13 +1195,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="16" t="s">
         <v>49</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>50</v>
       </c>
       <c r="E3" s="1"/>
     </row>
@@ -1194,10 +1213,10 @@
         <v>7</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -1209,10 +1228,10 @@
         <v>9</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5" s="1"/>
     </row>
@@ -1224,10 +1243,10 @@
         <v>10</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -1239,10 +1258,10 @@
         <v>13</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E7" s="1"/>
     </row>
@@ -1254,10 +1273,10 @@
         <v>15</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -1269,10 +1288,10 @@
         <v>17</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1"/>
     </row>
@@ -1284,10 +1303,10 @@
         <v>19</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -1299,10 +1318,10 @@
         <v>21</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -1314,10 +1333,10 @@
         <v>23</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2"/>
     </row>
@@ -1329,10 +1348,10 @@
         <v>25</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" s="1"/>
     </row>
@@ -1344,10 +1363,10 @@
         <v>27</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" s="2"/>
     </row>
@@ -1359,10 +1378,10 @@
         <v>29</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" s="1"/>
     </row>
@@ -1374,10 +1393,10 @@
         <v>31</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -1389,10 +1408,10 @@
         <v>33</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" s="1"/>
     </row>
@@ -1404,10 +1423,10 @@
         <v>35</v>
       </c>
       <c r="C18" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="17" t="s">
         <v>49</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>50</v>
       </c>
       <c r="E18" s="2"/>
     </row>
@@ -1419,10 +1438,10 @@
         <v>37</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E19" s="1"/>
     </row>
@@ -1434,10 +1453,10 @@
         <v>39</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E20" s="2"/>
     </row>
@@ -1446,48 +1465,48 @@
         <v>40</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="C21" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>49</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>50</v>
       </c>
       <c r="E21" s="9"/>
     </row>
     <row r="22" spans="1:6" ht="55.5" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>43</v>
-      </c>
       <c r="C22" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="82.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>45</v>
-      </c>
       <c r="C23" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E23" s="9"/>
     </row>

--- a/Taches.xlsx
+++ b/Taches.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DDJV\Projet\Projet1_Jeux_Video\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_jv\Projet1_Jeux_Video\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C325F0F8-0376-4F67-A099-A65F99BE273E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0C2A6B-16B1-4D72-8BCC-30FD30F2677B}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -314,10 +314,10 @@
     <t>tout le monde</t>
   </si>
   <si>
-    <t xml:space="preserve"> Tous ont 4 animations de déplacement (une pour chaque direction).:ok pour zombie</t>
-  </si>
-  <si>
     <t>Terminé</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -894,16 +894,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45B5B6CB-DB26-432C-9FC7-91B77E13F469}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.1796875" customWidth="1"/>
-    <col min="2" max="2" width="106.453125" customWidth="1"/>
-    <col min="3" max="3" width="57.08984375" customWidth="1"/>
-    <col min="4" max="4" width="36.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="77.6328125" customWidth="1"/>
+    <col min="1" max="1" width="41.21875" customWidth="1"/>
+    <col min="2" max="2" width="106.44140625" customWidth="1"/>
+    <col min="3" max="3" width="57.109375" customWidth="1"/>
+    <col min="4" max="4" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="77.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="55.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -920,7 +920,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="323.39999999999998" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" ht="323.39999999999998" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -928,14 +928,14 @@
         <v>5</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>52</v>
       </c>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="314.5" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:5" ht="306" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -950,7 +950,7 @@
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="56" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:5" ht="54.6" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -965,7 +965,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" ht="59.4" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:5" ht="59.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -980,7 +980,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" ht="220.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:5" ht="220.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>12</v>
       </c>
@@ -995,7 +995,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:5" ht="36.6" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" ht="56" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:5" ht="54.6" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -1018,14 +1018,14 @@
         <v>16</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>53</v>
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" ht="56" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:5" ht="54.6" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" ht="150" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:5" ht="150" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
@@ -1063,16 +1063,16 @@
         <v>22</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>48</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="36" x14ac:dyDescent="0.6">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
       <c r="A12" s="5" t="s">
         <v>23</v>
       </c>
@@ -1080,14 +1080,14 @@
         <v>24</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>48</v>
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
       <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
@@ -1095,14 +1095,14 @@
         <v>26</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>48</v>
       </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5" ht="36" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -1110,14 +1110,14 @@
         <v>28</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D14" s="20" t="s">
         <v>48</v>
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" ht="38.5" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:5" ht="37.799999999999997" x14ac:dyDescent="0.5">
       <c r="A15" s="4" t="s">
         <v>29</v>
       </c>
@@ -1125,14 +1125,14 @@
         <v>30</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>48</v>
       </c>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" ht="38.5" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:5" ht="37.799999999999997" x14ac:dyDescent="0.5">
       <c r="A16" s="6" t="s">
         <v>31</v>
       </c>
@@ -1140,14 +1140,14 @@
         <v>32</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>48</v>
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:6" ht="36" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:6" ht="36.6" x14ac:dyDescent="0.5">
       <c r="A17" s="3" t="s">
         <v>33</v>
       </c>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:6" ht="36" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:6" ht="36.6" x14ac:dyDescent="0.4">
       <c r="A18" s="6" t="s">
         <v>35</v>
       </c>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:6" ht="36" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:6" ht="36.6" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="56" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:6" ht="54.6" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
         <v>39</v>
       </c>
@@ -1200,14 +1200,14 @@
         <v>40</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>55</v>
       </c>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="1:6" ht="74" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" ht="72" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="E21" s="9"/>
     </row>
-    <row r="22" spans="1:6" ht="55.5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" ht="54" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>43</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="82.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="82.2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>45</v>
       </c>

--- a/Taches.xlsx
+++ b/Taches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Download\_Cours_Eddy\_prog_jv\Projet1_Jeux_Video\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0C2A6B-16B1-4D72-8BCC-30FD30F2677B}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D7B477-FE5A-4540-9336-C91C44C20E4A}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="61">
   <si>
     <t>Fonctionnalites</t>
   </si>
@@ -319,12 +319,15 @@
   <si>
     <t xml:space="preserve"> </t>
   </si>
+  <si>
+    <t>Faire des vauges de spawn progressif des enemis</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -373,13 +376,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="28"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -397,6 +393,22 @@
     <font>
       <b/>
       <sz val="26"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -491,7 +503,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -534,28 +546,34 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -893,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45B5B6CB-DB26-432C-9FC7-91B77E13F469}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.21875" customWidth="1"/>
@@ -904,19 +922,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="16" t="s">
         <v>49</v>
       </c>
     </row>
@@ -927,10 +945,10 @@
       <c r="B2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="20" t="s">
         <v>52</v>
       </c>
       <c r="E2" s="2"/>
@@ -942,10 +960,10 @@
       <c r="B3" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="21" t="s">
         <v>52</v>
       </c>
       <c r="E3" s="1"/>
@@ -957,10 +975,10 @@
       <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="20" t="s">
         <v>53</v>
       </c>
       <c r="E4" s="2"/>
@@ -972,10 +990,10 @@
       <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="20" t="s">
         <v>53</v>
       </c>
       <c r="E5" s="1"/>
@@ -987,10 +1005,10 @@
       <c r="B6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="20" t="s">
         <v>53</v>
       </c>
       <c r="E6" s="2"/>
@@ -1002,10 +1020,10 @@
       <c r="B7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="20" t="s">
         <v>53</v>
       </c>
       <c r="E7" s="1"/>
@@ -1017,10 +1035,10 @@
       <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="20" t="s">
         <v>53</v>
       </c>
       <c r="E8" s="2"/>
@@ -1032,10 +1050,10 @@
       <c r="B9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="20" t="s">
         <v>53</v>
       </c>
       <c r="E9" s="1"/>
@@ -1047,215 +1065,230 @@
       <c r="B10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="20" t="s">
         <v>53</v>
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" ht="150" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
       <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" ht="150" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C12" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D12" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
-      <c r="A12" s="5" t="s">
+    <row r="13" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
+      <c r="A13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B13" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C13" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D13" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
-      <c r="A13" s="3" t="s">
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
+      <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B14" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C14" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D14" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
-      <c r="A14" s="2" t="s">
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" ht="36.6" x14ac:dyDescent="0.5">
+      <c r="A15" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B15" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C15" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D15" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:5" ht="37.799999999999997" x14ac:dyDescent="0.5">
-      <c r="A15" s="4" t="s">
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" ht="37.799999999999997" x14ac:dyDescent="0.5">
+      <c r="A16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B16" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C16" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D16" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" ht="37.799999999999997" x14ac:dyDescent="0.5">
-      <c r="A16" s="6" t="s">
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" ht="37.799999999999997" x14ac:dyDescent="0.5">
+      <c r="A17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B17" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C17" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:6" ht="36.6" x14ac:dyDescent="0.5">
+      <c r="A18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D18" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" ht="36.6" x14ac:dyDescent="0.5">
-      <c r="A17" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="18" t="s">
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" ht="36.6" x14ac:dyDescent="0.4">
+      <c r="A19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" ht="36.6" x14ac:dyDescent="0.4">
-      <c r="A18" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="18" t="s">
+      <c r="D19" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:6" ht="36.6" x14ac:dyDescent="0.4">
+      <c r="A20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D20" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" ht="54.6" x14ac:dyDescent="0.4">
+      <c r="A21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" ht="36.6" x14ac:dyDescent="0.4">
-      <c r="A19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="18" t="s">
+      <c r="E22" s="9"/>
+    </row>
+    <row r="23" spans="1:6" ht="54" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D23" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="82.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:6" ht="54.6" x14ac:dyDescent="0.4">
-      <c r="A20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="9"/>
-    </row>
-    <row r="22" spans="1:6" ht="54" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="82.2" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23" s="9"/>
+      <c r="E24" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{69A9896E-8EAC-4EAC-8BD0-8B557D602AA3}"/>
@@ -1271,7 +1304,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C23" xr:uid="{10875831-33C7-4878-9CE7-6731C744575D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C24" xr:uid="{10875831-33C7-4878-9CE7-6731C744575D}">
       <formula1>"Pas commencé, En cours, Terminé"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Taches.xlsx
+++ b/Taches.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chacy\My Shit\Projet1_Jeux_Video\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chacy\My Shit\nbk\Projet1_Jeux_Video\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0764F5B-01F9-4A21-89DA-7CF035D32C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A82D4C-FBBE-489D-947F-D94CACF062F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="61">
   <si>
     <t>Fonctionnalites</t>
   </si>
@@ -314,7 +314,13 @@
     <t>tout le monde</t>
   </si>
   <si>
-    <t>Apparaît et bouge avec le joueur, reste à faire collisions</t>
+    <t>Reste a exploser quand entre en contact avec un enemi</t>
+  </si>
+  <si>
+    <t>Reste a exploser quand entre en contact avec un enemi + weird starting position</t>
+  </si>
+  <si>
+    <t>Reste a exploser quand entre en contact avec un enemi + finir seekEnemy</t>
   </si>
 </sst>
 </file>
@@ -992,7 +998,9 @@
       <c r="D6" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="22" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
@@ -1039,7 +1047,9 @@
       <c r="D9" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="23"/>
+      <c r="E9" s="22" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="57" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">

--- a/Taches.xlsx
+++ b/Taches.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chacy\My Shit\Projet1_Jeux_Video\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\Projet1_Jeux_Video\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0764F5B-01F9-4A21-89DA-7CF035D32C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54303BC5-CC77-4A97-98B9-DF6BB0AE0827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
+    <workbookView xWindow="840" yWindow="0" windowWidth="21600" windowHeight="15585" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="60">
   <si>
     <t>Fonctionnalites</t>
   </si>
@@ -43,19 +43,6 @@
   </si>
   <si>
     <t>Texte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niveau
-Un seul niveau bien conçu est demandé. On doit prendre soin d’avoir un visuel varié et soigné composé de plusieurs couches d’images. 
-1) Arrière-plan sur lequel le joueur marche (exemple : composition de gazon ou de terre).
-2) Doodads d’arrière-plan : petits objets décoratifs : plantes, cailloux, fleurs, etc.
-a. Au moins 3 différents non animés et fixe.
-b. Au moins 1 différent animé par du vent variable : ed :windsystem
-3) Doodads d’avant-plan animé : on doit voir minimum 2 entités (Exemple : nuages et oiseaux) se promener de gauche à droite à des vitesse variables. Ils doivent être petits ou semi-transparent afin de ne pas nuire à la visibilité du jeu.
-La limites de mouvement est de 3x3 la largeur de la grosseur de caméra que vous choisirez. Si le joueur dépasse cette limite, il est éliminé immédiatement.
-Cependant, quand le joueur près du bord de la carte, le visuel doit être adéquat pour 4x4 la largeur de la caméra.
-Exemple de conception adéquate : Une île bordée par de l’eau. Un donjon entouré de pics, une cave entourée de bras animées, etc.
-</t>
   </si>
   <si>
     <t>Joueur</t>
@@ -178,9 +165,6 @@
     <t xml:space="preserve">Gestion de la partie </t>
   </si>
   <si>
-    <t>Au démarrage du jeu, le joueur est placé au centre et tout est figé jusqu’à ce qu’on appuie sur la touche espace. La partie commence alors. La partie doit durer quelques minutes au plus et terminer si le joueur est éliminé ou s’il élimine le boss. Au moment que la partie se termine, détruire tous les ennemis et figer le joueur en jouant l’animation appropriée.</t>
-  </si>
-  <si>
     <t>Progression de difficulté</t>
   </si>
   <si>
@@ -194,6 +178,199 @@
 • Barre d’expérience dans le haut de l’écran ou au-dessus du joueur.</t>
   </si>
   <si>
+    <t>Eddy</t>
+  </si>
+  <si>
+    <t>Commentaires</t>
+  </si>
+  <si>
+    <t>En cours</t>
+  </si>
+  <si>
+    <t>Pas commencé</t>
+  </si>
+  <si>
+    <t>Antoine</t>
+  </si>
+  <si>
+    <t>Charlee</t>
+  </si>
+  <si>
+    <t>nb vies + vitesse</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>****</t>
+  </si>
+  <si>
+    <t>tout le monde</t>
+  </si>
+  <si>
+    <t>Apparaît et bouge avec le joueur, reste à faire collisions</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Niveau
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Un seul niveau bien conçu est demandé. On doit prendre soin d’avoir un visuel varié et soigné composé de plusieurs couches d’images. 
+1) Arrière-plan sur lequel le joueur marche (exemple : composition de gazon ou de terre).
+2) Doodads d’arrière-plan : petits objets décoratifs : plantes, cailloux, fleurs, etc.
+a. Au moins 3 différents non animés et fixe.
+b. Au moins 1 différent animé par du vent variable : ed :windsystem
+3) Doodads d’avant-plan animé : on doit voir minimum 2 entités (Exemple : nuages et oiseaux) se promener de gauche à droite à des vitesse variables. Ils doivent être petits ou semi-transparent afin de ne pas nuire à la visibilité du jeu.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La limites de mouvement est de 3x3 la largeur de la grosseur de caméra que vous choisirez. Si le joueur dépasse cette limite, il est éliminé immédiatement.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Cependant, quand le joueur près du bord de la carte, le visuel doit être adéquat pour 4x4 la largeur de la caméra.
+Exemple de conception adéquate : Une île bordée par de l’eau. Un donjon entouré de pics, une cave entourée de bras animées, etc.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Terminé</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Au démarrage du jeu, le joueur est placé au centre et tout est figé jusqu’à ce qu’on appuie sur la touche espace.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La partie commence alors.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La partie doit durer quelques minutes au plus et terminer si le joueur est éliminé</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ou s’il élimine le boss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Au moment que la partie se termine, détruire tous les ennemis et</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> figer le joueur en jouant l’animation appropriée.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -215,13 +392,113 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Attachez une Camera2D au joueur. Le joueur a 5 points de vie et commencera la partie avec une seule arme au choix. Si le joueur sort de la carte, il est automatiquement éliminé.
-• Animation
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Attachez une Camera2D au joueur. Le joueur a 5 points de vie et commencera la partie avec une seule arme au choix. Si le joueur sort de la carte, il est automatiquement éliminé.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>• Animation
 o Animation unique quand ne bouge pas.
-o 4 animations différentes pour les 4 directions. Trouvez un tween pour agrémenter le mouvement.
-o Animation unique lors d’une blessure accompagnée d’un tween.
-o Pour l’élimination, réutilisez l’animation unique de quand il ne bouge pas mais accompagnez le tout d’un tween et coloriez le joueur en rouge.
-o Pour la victoire, réutilisez l’animation unique de quand il ne bouge pas mais accompagnez le tout d’un tween et coloriez le joueur en vert.
+o 4 animations différentes pour les 4 directions. Trouvez un tween pour agrémenter le mouvement.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>o Animation unique lors d’une blessure accompagnée d’un tween.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>o Pour l’élimination, réutilisez l’animation unique de quand il ne bouge pas mais accompagnez le tout d’un tween et coloriez le joueur en rouge.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>o Pour la victoire, réutilisez l’animation unique de quand il ne bouge pas mais accompagnez le tout d’un tween et coloriez le joueur en vert.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -229,7 +506,7 @@
         <b/>
         <u/>
         <sz val="14"/>
-        <color theme="1"/>
+        <color rgb="FF00B050"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -240,7 +517,7 @@
       <rPr>
         <u/>
         <sz val="14"/>
-        <color theme="1"/>
+        <color rgb="FF00B050"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -251,7 +528,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <color theme="1"/>
+        <color rgb="FF00B050"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -282,46 +559,13 @@
       <t xml:space="preserve">
 </t>
     </r>
-  </si>
-  <si>
-    <t>Eddy</t>
-  </si>
-  <si>
-    <t>Commentaires</t>
-  </si>
-  <si>
-    <t>En cours</t>
-  </si>
-  <si>
-    <t>Pas commencé</t>
-  </si>
-  <si>
-    <t>Antoine</t>
-  </si>
-  <si>
-    <t>Charlee</t>
-  </si>
-  <si>
-    <t>nb vies + vitesse</t>
-  </si>
-  <si>
-    <t>Paul</t>
-  </si>
-  <si>
-    <t>****</t>
-  </si>
-  <si>
-    <t>tout le monde</t>
-  </si>
-  <si>
-    <t>Apparaît et bouge avec le joueur, reste à faire collisions</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,6 +639,44 @@
       <b/>
       <sz val="26"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="7"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -517,9 +799,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -555,6 +834,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -899,24 +1181,24 @@
     <col min="2" max="2" width="106.42578125" customWidth="1"/>
     <col min="3" max="3" width="57.140625" customWidth="1"/>
     <col min="4" max="4" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="77.5703125" style="24" customWidth="1"/>
+    <col min="5" max="5" width="77.5703125" style="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="55.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="21" t="s">
-        <v>49</v>
+      <c r="E1" s="20" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="323.45" customHeight="1" x14ac:dyDescent="0.35">
@@ -924,335 +1206,335 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="22"/>
+        <v>56</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="21"/>
     </row>
     <row r="3" spans="1:5" ht="337.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="23"/>
+        <v>59</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="22"/>
     </row>
     <row r="4" spans="1:5" ht="57" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="22"/>
+      <c r="C4" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="21"/>
     </row>
     <row r="5" spans="1:5" ht="59.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="22"/>
+    </row>
+    <row r="6" spans="1:5" ht="220.7" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="23"/>
-    </row>
-    <row r="6" spans="1:5" ht="220.7" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="22"/>
+      <c r="C6" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="21"/>
     </row>
     <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="23"/>
+      <c r="C7" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="22"/>
     </row>
     <row r="8" spans="1:5" ht="57" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>58</v>
+      <c r="E8" s="21" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="23"/>
+      <c r="C9" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="22"/>
     </row>
     <row r="10" spans="1:5" ht="57" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="22"/>
+      <c r="C10" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="21"/>
     </row>
     <row r="11" spans="1:5" ht="132.75" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="19" t="s">
+      <c r="C11" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="23"/>
+      <c r="D11" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="22"/>
     </row>
     <row r="12" spans="1:5" ht="36" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="22"/>
+      <c r="C12" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="21"/>
     </row>
     <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="19" t="s">
+      <c r="C13" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="23"/>
+      <c r="D13" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="22"/>
     </row>
     <row r="14" spans="1:5" ht="36" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="19" t="s">
+      <c r="C14" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="22"/>
+      <c r="D14" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="21"/>
     </row>
     <row r="15" spans="1:5" ht="57.75" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="19" t="s">
+      <c r="C15" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="23"/>
+      <c r="D15" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="22"/>
     </row>
     <row r="16" spans="1:5" ht="57.75" x14ac:dyDescent="0.4">
       <c r="A16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="19" t="s">
+      <c r="C16" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="22"/>
+      <c r="D16" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="21"/>
     </row>
     <row r="17" spans="1:6" ht="39" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="19" t="s">
+      <c r="C17" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="23"/>
+      <c r="D17" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="22"/>
     </row>
     <row r="18" spans="1:6" ht="36" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="22"/>
+      <c r="C18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="21"/>
     </row>
     <row r="19" spans="1:6" ht="36" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="23"/>
+      <c r="C19" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="22"/>
     </row>
     <row r="20" spans="1:6" ht="57" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" s="22"/>
+      <c r="C20" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="21"/>
     </row>
     <row r="21" spans="1:6" ht="75" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>51</v>
+        <v>58</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>47</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E21" s="8"/>
     </row>
     <row r="22" spans="1:6" ht="56.25" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>56</v>
+      <c r="F22" s="19" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="82.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E23" s="8"/>
     </row>

--- a/Taches.xlsx
+++ b/Taches.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\Projet1_Jeux_Video\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54303BC5-CC77-4A97-98B9-DF6BB0AE0827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF827F62-3903-4769-B1CA-B4E8F740B6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="840" yWindow="0" windowWidth="21600" windowHeight="15585" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -281,98 +281,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Au démarrage du jeu, le joueur est placé au centre et tout est figé jusqu’à ce qu’on appuie sur la touche espace.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>La partie commence alors.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>La partie doit durer quelques minutes au plus et terminer si le joueur est éliminé</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="7"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ou s’il élimine le boss</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Au moment que la partie se termine, détruire tous les ennemis et</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> figer le joueur en jouant l’animation appropriée.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <b/>
         <u/>
         <sz val="14"/>
@@ -558,6 +466,98 @@
       </rPr>
       <t xml:space="preserve">
 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Au démarrage du jeu, le joueur est placé au centre et tout est figé jusqu’à ce qu’on appuie sur la touche espace.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La partie commence alors.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La partie doit durer quelques minutes au plus et terminer si le joueur est éliminé</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ou s’il élimine le boss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Au moment que la partie se termine, détruire tous les ennemis et figer le joueur en jouant l’animation appropriée.</t>
     </r>
   </si>
 </sst>
@@ -1221,7 +1221,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>57</v>
@@ -1493,10 +1493,10 @@
         <v>40</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>49</v>
